--- a/payslip/FEB_2026_ANAKAPALLI_TL4P SALARY SHEET.xlsx
+++ b/payslip/FEB_2026_ANAKAPALLI_TL4P SALARY SHEET.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data For Account And Data Month Wise\2025-2026\Feb 2026\Dark Store\ANAKAPALLI AP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tbattula/fun/payslip/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1996DB2E-8FBB-4404-96EA-6DDB5BA0BDB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E3D271-B3DE-C848-9BDB-7331F5E03235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PIVOT TABLE" sheetId="59" state="hidden" r:id="rId1"/>
@@ -34,8 +34,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId12"/>
-    <pivotCache cacheId="1" r:id="rId13"/>
+    <pivotCache cacheId="23" r:id="rId12"/>
+    <pivotCache cacheId="24" r:id="rId13"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1183,7 +1183,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Total Invoice Value in Rs. 1,95,843/-, In Words …Rupees One Lakh Ninety Five Thusand Eight</t>
@@ -1193,7 +1193,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -1204,7 +1204,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Hundred Forty Three Only</t>
@@ -1285,7 +1285,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>GST No.-</t>
     </r>
@@ -1294,7 +1294,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1303,7 +1303,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>37AAJCR6636B1ZB</t>
     </r>
@@ -1824,17 +1824,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
-    <numFmt numFmtId="44" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="[$-409]d/mmm/yy;@"/>
-    <numFmt numFmtId="168" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="169" formatCode="0_ "/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="172" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="[$-409]d/mmm/yy;@"/>
+    <numFmt numFmtId="167" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="168" formatCode="0_ "/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="171" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="54">
+  <fonts count="54" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1847,34 +1847,34 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1887,14 +1887,14 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1902,41 +1902,41 @@
       <sz val="11"/>
       <color rgb="FF00B050"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color indexed="8"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1944,7 +1944,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1952,27 +1952,27 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -1980,38 +1980,38 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2024,7 +2024,7 @@
       <sz val="22"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2032,7 +2032,7 @@
       <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2040,7 +2040,7 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2049,7 +2049,7 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2057,7 +2057,7 @@
       <sz val="8"/>
       <color theme="0" tint="-4.9989318521683403E-2"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2065,14 +2065,14 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2080,7 +2080,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2088,28 +2088,28 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2117,7 +2117,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2130,82 +2130,82 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="15">
@@ -2789,7 +2789,7 @@
   </borders>
   <cellStyleXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="38" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="45" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="46" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="47" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2873,7 +2873,7 @@
     <xf numFmtId="1" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3020,19 +3020,19 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="18" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3083,8 +3083,8 @@
     <xf numFmtId="0" fontId="21" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3093,7 +3093,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3121,8 +3121,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
@@ -3155,10 +3155,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="33" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="33" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -3245,7 +3245,7 @@
     <xf numFmtId="1" fontId="36" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -3261,17 +3261,17 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="12" fillId="0" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3378,19 +3378,19 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="15" fillId="2" borderId="1" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="15" fillId="2" borderId="1" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="15" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="15" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="15" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
@@ -3421,27 +3421,6 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="10" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="10" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="10" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3450,6 +3429,27 @@
     </xf>
     <xf numFmtId="0" fontId="35" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="10" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="10" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="10" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3502,6 +3502,60 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3525,60 +3579,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -10036,7 +10036,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000001000000}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000001000000}" name="PivotTable1" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="B3:E6" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="53">
     <pivotField showAll="0"/>
@@ -10145,7 +10145,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable2" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="B10:E13" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="53">
     <pivotField showAll="0"/>
@@ -10512,16 +10512,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:E15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="15.85546875" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" customWidth="1"/>
-    <col min="4" max="4" width="27.42578125" customWidth="1"/>
+    <col min="1" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.1640625" customWidth="1"/>
+    <col min="4" max="4" width="27.5" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="20.42578125" customWidth="1"/>
+    <col min="6" max="6" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -10535,7 +10535,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:5">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B4" s="190" t="s">
         <v>4</v>
       </c>
@@ -10549,7 +10549,7 @@
         <v>52141.962500000001</v>
       </c>
     </row>
-    <row r="5" spans="2:5">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B5" s="190" t="s">
         <v>5</v>
       </c>
@@ -10563,7 +10563,7 @@
         <v>14427.205</v>
       </c>
     </row>
-    <row r="6" spans="2:5">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B6" s="190" t="s">
         <v>6</v>
       </c>
@@ -10577,16 +10577,16 @@
         <v>66569.167499999996</v>
       </c>
     </row>
-    <row r="7" spans="2:5">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
       <c r="E7" s="96"/>
     </row>
-    <row r="8" spans="2:5">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
       <c r="E8" s="96" t="e">
         <f>GETPIVOTDATA("Sum of CTC",$B$3)-#REF!</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="10" spans="2:5">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>0</v>
       </c>
@@ -10600,7 +10600,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="2:5">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B11" s="190" t="s">
         <v>4</v>
       </c>
@@ -10614,7 +10614,7 @@
         <v>91497.35</v>
       </c>
     </row>
-    <row r="12" spans="2:5">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B12" s="190" t="s">
         <v>5</v>
       </c>
@@ -10628,7 +10628,7 @@
         <v>19378.8475</v>
       </c>
     </row>
-    <row r="13" spans="2:5">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B13" s="190" t="s">
         <v>6</v>
       </c>
@@ -10642,7 +10642,7 @@
         <v>110876.19749999999</v>
       </c>
     </row>
-    <row r="15" spans="2:5">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
       <c r="E15" s="96">
         <f>GETPIVOTDATA("Sum of CTC",$B$10)-'Wage Sheet'!AS21</f>
         <v>-130218.49249999999</v>
@@ -10656,41 +10656,41 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AE15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" customWidth="1"/>
-    <col min="5" max="5" width="25.85546875" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="2" max="2" width="21.83203125" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" customWidth="1"/>
+    <col min="5" max="5" width="25.83203125" customWidth="1"/>
+    <col min="6" max="6" width="16.1640625" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" customWidth="1"/>
     <col min="8" max="8" width="30" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" customWidth="1"/>
-    <col min="10" max="10" width="15.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" customWidth="1"/>
-    <col min="12" max="12" width="5.7109375" customWidth="1"/>
-    <col min="14" max="14" width="6.140625" customWidth="1"/>
+    <col min="9" max="9" width="10.5" customWidth="1"/>
+    <col min="10" max="10" width="15.83203125" customWidth="1"/>
+    <col min="11" max="11" width="6.6640625" customWidth="1"/>
+    <col min="12" max="12" width="5.6640625" customWidth="1"/>
+    <col min="14" max="14" width="6.1640625" customWidth="1"/>
     <col min="15" max="15" width="7" customWidth="1"/>
-    <col min="16" max="16" width="7.140625" customWidth="1"/>
-    <col min="17" max="17" width="8.85546875" customWidth="1"/>
-    <col min="18" max="18" width="8.140625" customWidth="1"/>
+    <col min="16" max="16" width="7.1640625" customWidth="1"/>
+    <col min="17" max="17" width="8.83203125" customWidth="1"/>
+    <col min="18" max="18" width="8.1640625" customWidth="1"/>
     <col min="19" max="19" width="7" customWidth="1"/>
-    <col min="20" max="20" width="6.7109375" customWidth="1"/>
-    <col min="21" max="21" width="7.140625" customWidth="1"/>
-    <col min="22" max="22" width="8.5703125" customWidth="1"/>
-    <col min="23" max="23" width="6.85546875" customWidth="1"/>
-    <col min="24" max="24" width="5.42578125" customWidth="1"/>
-    <col min="25" max="25" width="6.85546875" customWidth="1"/>
+    <col min="20" max="20" width="6.6640625" customWidth="1"/>
+    <col min="21" max="21" width="7.1640625" customWidth="1"/>
+    <col min="22" max="22" width="8.5" customWidth="1"/>
+    <col min="23" max="23" width="6.83203125" customWidth="1"/>
+    <col min="24" max="24" width="5.5" customWidth="1"/>
+    <col min="25" max="25" width="6.83203125" customWidth="1"/>
     <col min="26" max="26" width="8" customWidth="1"/>
-    <col min="27" max="27" width="4.85546875" customWidth="1"/>
+    <col min="27" max="27" width="4.83203125" customWidth="1"/>
     <col min="28" max="28" width="8" customWidth="1"/>
-    <col min="29" max="29" width="7.140625" customWidth="1"/>
-    <col min="30" max="30" width="7.5703125" customWidth="1"/>
-    <col min="31" max="31" width="56.42578125" customWidth="1"/>
+    <col min="29" max="29" width="7.1640625" customWidth="1"/>
+    <col min="30" max="30" width="7.5" customWidth="1"/>
+    <col min="31" max="31" width="56.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="38.25">
+    <row r="1" spans="1:31" ht="45" x14ac:dyDescent="0.2">
       <c r="A1" s="254" t="s">
         <v>7</v>
       </c>
@@ -10785,7 +10785,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -10904,7 +10904,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -11023,7 +11023,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -11142,7 +11142,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -11261,7 +11261,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -11380,7 +11380,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -11499,7 +11499,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -11618,7 +11618,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A9" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -11737,7 +11737,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A10" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -11856,7 +11856,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A11">
         <f>'Left Employee'!A50</f>
         <v>9</v>
@@ -11975,7 +11975,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A12">
         <f>'Left Employee'!A51</f>
         <v>10</v>
@@ -12094,7 +12094,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A13" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -12213,7 +12213,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A14" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -12332,7 +12332,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A15" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -12463,28 +12463,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AN19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" style="189" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" customWidth="1"/>
-    <col min="7" max="10" width="6.5703125" style="189" customWidth="1"/>
-    <col min="11" max="11" width="7.28515625" style="189" customWidth="1"/>
-    <col min="12" max="22" width="6.5703125" style="189" customWidth="1"/>
-    <col min="23" max="23" width="7.28515625" style="189" customWidth="1"/>
-    <col min="24" max="24" width="7.140625" style="189" customWidth="1"/>
-    <col min="25" max="34" width="6.5703125" style="189" customWidth="1"/>
-    <col min="35" max="35" width="8.5703125" customWidth="1"/>
-    <col min="36" max="36" width="6.42578125" customWidth="1"/>
+    <col min="2" max="2" width="15.1640625" customWidth="1"/>
+    <col min="3" max="3" width="22.5" customWidth="1"/>
+    <col min="4" max="4" width="11.5" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" style="189" customWidth="1"/>
+    <col min="6" max="6" width="10.1640625" customWidth="1"/>
+    <col min="7" max="10" width="6.5" style="189" customWidth="1"/>
+    <col min="11" max="11" width="7.33203125" style="189" customWidth="1"/>
+    <col min="12" max="22" width="6.5" style="189" customWidth="1"/>
+    <col min="23" max="23" width="7.33203125" style="189" customWidth="1"/>
+    <col min="24" max="24" width="7.1640625" style="189" customWidth="1"/>
+    <col min="25" max="34" width="6.5" style="189" customWidth="1"/>
+    <col min="35" max="35" width="8.5" customWidth="1"/>
+    <col min="36" max="36" width="6.5" customWidth="1"/>
     <col min="37" max="38" width="7" customWidth="1"/>
-    <col min="39" max="39" width="7.85546875" customWidth="1"/>
-    <col min="40" max="40" width="5.5703125" customWidth="1"/>
+    <col min="39" max="39" width="7.83203125" customWidth="1"/>
+    <col min="40" max="40" width="5.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C1" s="236" t="s">
         <v>105</v>
       </c>
@@ -12492,23 +12492,23 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="2" spans="1:40">
-      <c r="A2" s="276" t="s">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A2" s="283" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="278" t="s">
+      <c r="B2" s="281" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="280" t="s">
+      <c r="C2" s="285" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="280" t="s">
+      <c r="D2" s="285" t="s">
         <v>109</v>
       </c>
-      <c r="E2" s="276" t="s">
+      <c r="E2" s="283" t="s">
         <v>110</v>
       </c>
-      <c r="F2" s="278" t="s">
+      <c r="F2" s="281" t="s">
         <v>111</v>
       </c>
       <c r="G2" s="238">
@@ -12623,32 +12623,32 @@
         <f t="shared" si="0"/>
         <v>46081</v>
       </c>
-      <c r="AI2" s="281" t="s">
+      <c r="AI2" s="279" t="s">
         <v>112</v>
       </c>
-      <c r="AJ2" s="281" t="s">
+      <c r="AJ2" s="279" t="s">
         <v>113</v>
       </c>
-      <c r="AK2" s="281" t="s">
+      <c r="AK2" s="279" t="s">
         <v>114</v>
       </c>
-      <c r="AL2" s="281" t="s">
+      <c r="AL2" s="279" t="s">
         <v>115</v>
       </c>
-      <c r="AM2" s="281" t="s">
+      <c r="AM2" s="279" t="s">
         <v>116</v>
       </c>
-      <c r="AN2" s="281" t="s">
+      <c r="AN2" s="279" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="3" spans="1:40">
-      <c r="A3" s="277"/>
-      <c r="B3" s="279"/>
-      <c r="C3" s="277"/>
-      <c r="D3" s="277"/>
-      <c r="E3" s="277"/>
-      <c r="F3" s="279"/>
+    <row r="3" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A3" s="284"/>
+      <c r="B3" s="282"/>
+      <c r="C3" s="284"/>
+      <c r="D3" s="284"/>
+      <c r="E3" s="284"/>
+      <c r="F3" s="282"/>
       <c r="G3" s="239" t="str">
         <f>TEXT(G2,"DDD")</f>
         <v>Sun</v>
@@ -12761,14 +12761,14 @@
         <f t="shared" si="1"/>
         <v>Sat</v>
       </c>
-      <c r="AI3" s="282"/>
-      <c r="AJ3" s="282"/>
-      <c r="AK3" s="282"/>
-      <c r="AL3" s="282"/>
-      <c r="AM3" s="282"/>
-      <c r="AN3" s="282"/>
+      <c r="AI3" s="280"/>
+      <c r="AJ3" s="280"/>
+      <c r="AK3" s="280"/>
+      <c r="AL3" s="280"/>
+      <c r="AM3" s="280"/>
+      <c r="AN3" s="280"/>
     </row>
-    <row r="4" spans="1:40" ht="15.75">
+    <row r="4" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="240">
         <v>1</v>
       </c>
@@ -12896,7 +12896,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:40" ht="15.75">
+    <row r="5" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="240">
         <v>2</v>
       </c>
@@ -13024,7 +13024,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:40" ht="15.75">
+    <row r="6" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="240">
         <v>3</v>
       </c>
@@ -13152,7 +13152,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:40" ht="15.75">
+    <row r="7" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="240">
         <v>4</v>
       </c>
@@ -13280,7 +13280,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:40" ht="15.75">
+    <row r="8" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="240">
         <v>5</v>
       </c>
@@ -13408,7 +13408,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:40" ht="15.75">
+    <row r="9" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="240">
         <v>6</v>
       </c>
@@ -13536,7 +13536,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:40" ht="15.75">
+    <row r="10" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="240">
         <v>7</v>
       </c>
@@ -13664,7 +13664,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:40" ht="15.75">
+    <row r="11" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="240">
         <v>8</v>
       </c>
@@ -13792,7 +13792,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:40" ht="15.75">
+    <row r="12" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="240">
         <v>9</v>
       </c>
@@ -13920,7 +13920,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:40" ht="15.75">
+    <row r="13" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="240">
         <v>10</v>
       </c>
@@ -14048,7 +14048,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:40" ht="15.75">
+    <row r="14" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="240">
         <v>11</v>
       </c>
@@ -14176,7 +14176,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:40" ht="15.75">
+    <row r="15" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="240">
         <v>12</v>
       </c>
@@ -14304,7 +14304,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:40" ht="15.75">
+    <row r="16" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="240">
         <v>13</v>
       </c>
@@ -14432,7 +14432,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:40" ht="15.75">
+    <row r="17" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="240">
         <v>14</v>
       </c>
@@ -14560,7 +14560,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:40" ht="15.75">
+    <row r="18" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="240">
         <v>15</v>
       </c>
@@ -14688,7 +14688,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:40" ht="15.75">
+    <row r="19" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="B19" s="249"/>
       <c r="AI19" s="253">
         <f>SUM(AI4:AI18)</f>
@@ -14717,6 +14717,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
     <mergeCell ref="AM2:AM3"/>
     <mergeCell ref="AN2:AN3"/>
     <mergeCell ref="F2:F3"/>
@@ -14724,11 +14729,6 @@
     <mergeCell ref="AJ2:AJ3"/>
     <mergeCell ref="AK2:AK3"/>
     <mergeCell ref="AL2:AL3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:B18">
     <cfRule type="duplicateValues" dxfId="99" priority="384"/>
@@ -14744,47 +14744,47 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:BY30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" style="189" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" customWidth="1"/>
-    <col min="3" max="3" width="19.85546875" style="189" customWidth="1"/>
-    <col min="4" max="4" width="26.7109375" customWidth="1"/>
-    <col min="5" max="5" width="35.5703125" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" style="189" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" customWidth="1"/>
+    <col min="3" max="3" width="19.83203125" style="189" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" customWidth="1"/>
+    <col min="5" max="5" width="35.5" customWidth="1"/>
+    <col min="6" max="6" width="11.1640625" customWidth="1"/>
     <col min="7" max="7" width="17" style="189" customWidth="1"/>
-    <col min="8" max="8" width="17.140625" style="189" customWidth="1"/>
+    <col min="8" max="8" width="17.1640625" style="189" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
-    <col min="11" max="11" width="7.140625" style="189" customWidth="1"/>
-    <col min="12" max="12" width="15.5703125" style="189" customWidth="1"/>
-    <col min="13" max="13" width="16.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.5" customWidth="1"/>
+    <col min="11" max="11" width="7.1640625" style="189" customWidth="1"/>
+    <col min="12" max="12" width="15.5" style="189" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" customWidth="1"/>
     <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="10" customWidth="1"/>
     <col min="16" max="16" width="6" style="189" customWidth="1"/>
-    <col min="17" max="17" width="11.42578125" style="189" customWidth="1"/>
+    <col min="17" max="17" width="11.5" style="189" customWidth="1"/>
     <col min="18" max="24" width="9" style="189" customWidth="1"/>
     <col min="25" max="27" width="9" customWidth="1"/>
     <col min="28" max="35" width="9" style="189" customWidth="1"/>
-    <col min="36" max="36" width="10.5703125" style="189" customWidth="1"/>
+    <col min="36" max="36" width="10.5" style="189" customWidth="1"/>
     <col min="37" max="42" width="9" style="189" customWidth="1"/>
-    <col min="43" max="43" width="11.140625" style="189" customWidth="1"/>
+    <col min="43" max="43" width="11.1640625" style="189" customWidth="1"/>
     <col min="44" max="44" width="9" style="189" customWidth="1"/>
-    <col min="45" max="45" width="8.7109375" style="189" customWidth="1"/>
+    <col min="45" max="45" width="8.6640625" style="189" customWidth="1"/>
     <col min="46" max="49" width="9" style="189" customWidth="1"/>
-    <col min="50" max="50" width="10.140625" style="189" customWidth="1"/>
-    <col min="51" max="51" width="8.7109375" style="189" customWidth="1"/>
-    <col min="53" max="53" width="34.85546875" customWidth="1"/>
-    <col min="54" max="54" width="21.42578125" style="190" customWidth="1"/>
-    <col min="55" max="55" width="15.42578125" customWidth="1"/>
+    <col min="50" max="50" width="10.1640625" style="189" customWidth="1"/>
+    <col min="51" max="51" width="8.6640625" style="189" customWidth="1"/>
+    <col min="53" max="53" width="34.83203125" customWidth="1"/>
+    <col min="54" max="54" width="21.5" style="190" customWidth="1"/>
+    <col min="55" max="55" width="15.5" customWidth="1"/>
     <col min="61" max="73" width="6" customWidth="1"/>
-    <col min="74" max="74" width="7.85546875" customWidth="1"/>
+    <col min="74" max="74" width="7.83203125" customWidth="1"/>
     <col min="75" max="75" width="10" customWidth="1"/>
-    <col min="76" max="76" width="8.140625" customWidth="1"/>
+    <col min="76" max="76" width="8.1640625" customWidth="1"/>
     <col min="77" max="77" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:77" s="187" customFormat="1">
+    <row r="1" spans="1:77" s="187" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="191" t="s">
         <v>163</v>
       </c>
@@ -14847,7 +14847,7 @@
       <c r="BF1" s="192"/>
       <c r="BG1" s="192"/>
     </row>
-    <row r="2" spans="1:77" s="187" customFormat="1">
+    <row r="2" spans="1:77" s="187" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="191" t="s">
         <v>164</v>
       </c>
@@ -14910,7 +14910,7 @@
       <c r="BF2" s="192"/>
       <c r="BG2" s="192"/>
     </row>
-    <row r="3" spans="1:77" s="187" customFormat="1" ht="15.75">
+    <row r="3" spans="1:77" s="187" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A3" s="195" t="s">
         <v>165</v>
       </c>
@@ -14972,25 +14972,25 @@
       <c r="BE3" s="192"/>
       <c r="BF3" s="192"/>
       <c r="BG3" s="192"/>
-      <c r="BI3" s="283" t="s">
+      <c r="BI3" s="276" t="s">
         <v>166</v>
       </c>
-      <c r="BJ3" s="284"/>
-      <c r="BK3" s="284"/>
-      <c r="BL3" s="284"/>
-      <c r="BM3" s="284"/>
-      <c r="BN3" s="284"/>
-      <c r="BO3" s="284"/>
-      <c r="BP3" s="285"/>
-      <c r="BQ3" s="283" t="s">
+      <c r="BJ3" s="277"/>
+      <c r="BK3" s="277"/>
+      <c r="BL3" s="277"/>
+      <c r="BM3" s="277"/>
+      <c r="BN3" s="277"/>
+      <c r="BO3" s="277"/>
+      <c r="BP3" s="278"/>
+      <c r="BQ3" s="276" t="s">
         <v>167</v>
       </c>
-      <c r="BR3" s="284"/>
-      <c r="BS3" s="284"/>
-      <c r="BT3" s="284"/>
-      <c r="BU3" s="285"/>
+      <c r="BR3" s="277"/>
+      <c r="BS3" s="277"/>
+      <c r="BT3" s="277"/>
+      <c r="BU3" s="278"/>
     </row>
-    <row r="4" spans="1:77" s="188" customFormat="1" ht="70.5" customHeight="1">
+    <row r="4" spans="1:77" s="188" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="196" t="s">
         <v>168</v>
       </c>
@@ -15218,7 +15218,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="5" spans="1:77" s="2" customFormat="1" ht="15.75">
+    <row r="5" spans="1:77" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="36">
         <v>1</v>
       </c>
@@ -15428,7 +15428,7 @@
       <c r="BX5" s="16"/>
       <c r="BY5" s="16"/>
     </row>
-    <row r="6" spans="1:77" s="2" customFormat="1" ht="15.75" customHeight="1">
+    <row r="6" spans="1:77" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="36">
         <v>2</v>
       </c>
@@ -15638,7 +15638,7 @@
       <c r="BX6" s="16"/>
       <c r="BY6" s="16"/>
     </row>
-    <row r="7" spans="1:77" s="2" customFormat="1" ht="15.75">
+    <row r="7" spans="1:77" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="36">
         <v>3</v>
       </c>
@@ -15848,7 +15848,7 @@
       <c r="BX7" s="16"/>
       <c r="BY7" s="16"/>
     </row>
-    <row r="8" spans="1:77" s="2" customFormat="1" ht="15.75">
+    <row r="8" spans="1:77" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="36">
         <v>4</v>
       </c>
@@ -16058,7 +16058,7 @@
       <c r="BX8" s="16"/>
       <c r="BY8" s="16"/>
     </row>
-    <row r="9" spans="1:77" s="2" customFormat="1" ht="15.75">
+    <row r="9" spans="1:77" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="36">
         <v>5</v>
       </c>
@@ -16268,7 +16268,7 @@
       <c r="BX9" s="16"/>
       <c r="BY9" s="16"/>
     </row>
-    <row r="10" spans="1:77" s="2" customFormat="1" ht="15.75">
+    <row r="10" spans="1:77" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="36">
         <v>6</v>
       </c>
@@ -16478,7 +16478,7 @@
       <c r="BX10" s="16"/>
       <c r="BY10" s="16"/>
     </row>
-    <row r="11" spans="1:77" s="2" customFormat="1" ht="15.75">
+    <row r="11" spans="1:77" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="36">
         <v>7</v>
       </c>
@@ -16688,7 +16688,7 @@
       <c r="BX11" s="16"/>
       <c r="BY11" s="16"/>
     </row>
-    <row r="12" spans="1:77" s="2" customFormat="1" ht="15.75">
+    <row r="12" spans="1:77" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="36">
         <v>8</v>
       </c>
@@ -16898,7 +16898,7 @@
       <c r="BX12" s="16"/>
       <c r="BY12" s="16"/>
     </row>
-    <row r="13" spans="1:77" s="2" customFormat="1" ht="15.75">
+    <row r="13" spans="1:77" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="36">
         <v>9</v>
       </c>
@@ -17108,7 +17108,7 @@
       <c r="BX13" s="16"/>
       <c r="BY13" s="16"/>
     </row>
-    <row r="14" spans="1:77" s="2" customFormat="1" ht="15.75">
+    <row r="14" spans="1:77" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="36">
         <v>10</v>
       </c>
@@ -17318,7 +17318,7 @@
       <c r="BX14" s="16"/>
       <c r="BY14" s="16"/>
     </row>
-    <row r="15" spans="1:77" s="2" customFormat="1" ht="15.75">
+    <row r="15" spans="1:77" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="36">
         <v>11</v>
       </c>
@@ -17528,7 +17528,7 @@
       <c r="BX15" s="16"/>
       <c r="BY15" s="16"/>
     </row>
-    <row r="16" spans="1:77" s="2" customFormat="1" ht="15.75">
+    <row r="16" spans="1:77" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="36">
         <v>12</v>
       </c>
@@ -17738,7 +17738,7 @@
       <c r="BX16" s="16"/>
       <c r="BY16" s="16"/>
     </row>
-    <row r="17" spans="1:77" s="2" customFormat="1" ht="15.75">
+    <row r="17" spans="1:77" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="36">
         <v>13</v>
       </c>
@@ -17948,7 +17948,7 @@
       <c r="BX17" s="16"/>
       <c r="BY17" s="16"/>
     </row>
-    <row r="18" spans="1:77" s="2" customFormat="1" ht="18" customHeight="1">
+    <row r="18" spans="1:77" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="36">
         <v>14</v>
       </c>
@@ -18158,7 +18158,7 @@
       <c r="BX18" s="16"/>
       <c r="BY18" s="16"/>
     </row>
-    <row r="19" spans="1:77" s="2" customFormat="1" ht="18" customHeight="1">
+    <row r="19" spans="1:77" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="36">
         <v>15</v>
       </c>
@@ -18368,7 +18368,7 @@
       <c r="BX19" s="16"/>
       <c r="BY19" s="16"/>
     </row>
-    <row r="20" spans="1:77">
+    <row r="20" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A20" s="36"/>
       <c r="B20" s="9"/>
       <c r="C20" s="206"/>
@@ -18445,7 +18445,7 @@
       <c r="BX20" s="8"/>
       <c r="BY20" s="8"/>
     </row>
-    <row r="21" spans="1:77" s="96" customFormat="1" ht="15.75">
+    <row r="21" spans="1:77" s="96" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="209"/>
       <c r="C21" s="209"/>
       <c r="G21" s="209"/>
@@ -18610,11 +18610,11 @@
         <v>187271</v>
       </c>
     </row>
-    <row r="22" spans="1:77">
+    <row r="22" spans="1:77" x14ac:dyDescent="0.2">
       <c r="G22" s="209"/>
       <c r="Q22" s="209"/>
     </row>
-    <row r="23" spans="1:77">
+    <row r="23" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B23" s="210"/>
       <c r="G23" s="209"/>
       <c r="P23" s="209"/>
@@ -18627,7 +18627,7 @@
       <c r="BE23" s="96"/>
       <c r="BF23" s="96"/>
     </row>
-    <row r="24" spans="1:77">
+    <row r="24" spans="1:77" x14ac:dyDescent="0.2">
       <c r="G24" s="209"/>
       <c r="Q24" s="209"/>
       <c r="AR24" s="221"/>
@@ -18636,7 +18636,7 @@
       <c r="AX24" s="221"/>
       <c r="BF24" s="96"/>
     </row>
-    <row r="25" spans="1:77">
+    <row r="25" spans="1:77" x14ac:dyDescent="0.2">
       <c r="Q25" s="209"/>
       <c r="Z25" s="97"/>
       <c r="AA25" s="97"/>
@@ -18650,25 +18650,25 @@
       <c r="BE25" s="96"/>
       <c r="BF25" s="96"/>
     </row>
-    <row r="26" spans="1:77">
+    <row r="26" spans="1:77" x14ac:dyDescent="0.2">
       <c r="Q26" s="209"/>
       <c r="AJ26" s="221"/>
       <c r="AP26" s="209"/>
       <c r="AS26" s="221"/>
       <c r="AY26" s="221"/>
     </row>
-    <row r="27" spans="1:77">
+    <row r="27" spans="1:77" x14ac:dyDescent="0.2">
       <c r="AP27" s="209"/>
       <c r="AS27" s="221"/>
     </row>
-    <row r="28" spans="1:77">
+    <row r="28" spans="1:77" x14ac:dyDescent="0.2">
       <c r="AP28" s="209"/>
     </row>
-    <row r="29" spans="1:77">
+    <row r="29" spans="1:77" x14ac:dyDescent="0.2">
       <c r="AP29" s="209"/>
       <c r="AS29" s="209"/>
     </row>
-    <row r="30" spans="1:77">
+    <row r="30" spans="1:77" x14ac:dyDescent="0.2">
       <c r="AP30" s="209"/>
       <c r="AS30" s="209"/>
     </row>
@@ -18763,18 +18763,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:G54"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" customWidth="1"/>
-    <col min="4" max="4" width="31.85546875" customWidth="1"/>
-    <col min="5" max="5" width="28.5703125" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" customWidth="1"/>
-    <col min="7" max="7" width="6.28515625" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" customWidth="1"/>
+    <col min="3" max="3" width="23.1640625" customWidth="1"/>
+    <col min="4" max="4" width="31.83203125" customWidth="1"/>
+    <col min="5" max="5" width="28.5" customWidth="1"/>
+    <col min="6" max="6" width="21.83203125" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="28.5">
+    <row r="2" spans="2:7" ht="29" x14ac:dyDescent="0.35">
       <c r="B2" s="156"/>
       <c r="C2" s="286" t="s">
         <v>163</v>
@@ -18784,7 +18784,7 @@
       <c r="F2" s="286"/>
       <c r="G2" s="157"/>
     </row>
-    <row r="3" spans="2:7" ht="15.75">
+    <row r="3" spans="2:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B3" s="158"/>
       <c r="C3" s="287" t="s">
         <v>303</v>
@@ -18794,7 +18794,7 @@
       <c r="F3" s="287"/>
       <c r="G3" s="159"/>
     </row>
-    <row r="4" spans="2:7" ht="21">
+    <row r="4" spans="2:7" ht="21" x14ac:dyDescent="0.25">
       <c r="B4" s="158"/>
       <c r="C4" s="288" t="s">
         <v>304</v>
@@ -18804,7 +18804,7 @@
       <c r="F4" s="288"/>
       <c r="G4" s="159"/>
     </row>
-    <row r="5" spans="2:7" ht="16.899999999999999" customHeight="1">
+    <row r="5" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="158"/>
       <c r="C5" s="160"/>
       <c r="D5" s="161" t="s">
@@ -18818,7 +18818,7 @@
       </c>
       <c r="G5" s="159"/>
     </row>
-    <row r="6" spans="2:7" ht="18.75">
+    <row r="6" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B6" s="158"/>
       <c r="C6" s="164" t="s">
         <v>306</v>
@@ -18836,7 +18836,7 @@
       </c>
       <c r="G6" s="159"/>
     </row>
-    <row r="7" spans="2:7" ht="18.75">
+    <row r="7" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B7" s="158"/>
       <c r="C7" s="164" t="s">
         <v>179</v>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="G7" s="159"/>
     </row>
-    <row r="8" spans="2:7" ht="18.75">
+    <row r="8" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B8" s="158"/>
       <c r="C8" s="164" t="s">
         <v>309</v>
@@ -18872,7 +18872,7 @@
       </c>
       <c r="G8" s="159"/>
     </row>
-    <row r="9" spans="2:7" ht="18.75" hidden="1">
+    <row r="9" spans="2:7" ht="19" hidden="1" x14ac:dyDescent="0.25">
       <c r="B9" s="158"/>
       <c r="C9" s="167" t="s">
         <v>311</v>
@@ -18890,7 +18890,7 @@
       </c>
       <c r="G9" s="159"/>
     </row>
-    <row r="10" spans="2:7">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="158"/>
       <c r="C10" s="169"/>
       <c r="D10" s="169"/>
@@ -18898,7 +18898,7 @@
       <c r="F10" s="169"/>
       <c r="G10" s="159"/>
     </row>
-    <row r="11" spans="2:7" ht="18.75">
+    <row r="11" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B11" s="158"/>
       <c r="C11" s="170" t="s">
         <v>313</v>
@@ -18910,7 +18910,7 @@
       <c r="F11" s="171"/>
       <c r="G11" s="159"/>
     </row>
-    <row r="12" spans="2:7" ht="18.75">
+    <row r="12" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B12" s="158"/>
       <c r="C12" s="172" t="s">
         <v>315</v>
@@ -18928,7 +18928,7 @@
       </c>
       <c r="G12" s="159"/>
     </row>
-    <row r="13" spans="2:7" ht="18.75">
+    <row r="13" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B13" s="158"/>
       <c r="C13" s="172" t="s">
         <v>317</v>
@@ -18946,7 +18946,7 @@
       </c>
       <c r="G13" s="159"/>
     </row>
-    <row r="14" spans="2:7" ht="18.75">
+    <row r="14" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B14" s="158"/>
       <c r="C14" s="172" t="s">
         <v>319</v>
@@ -18964,7 +18964,7 @@
       </c>
       <c r="G14" s="159"/>
     </row>
-    <row r="15" spans="2:7" ht="18.75">
+    <row r="15" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B15" s="158"/>
       <c r="C15" s="172" t="s">
         <v>321</v>
@@ -18982,7 +18982,7 @@
       </c>
       <c r="G15" s="159"/>
     </row>
-    <row r="16" spans="2:7" ht="18.75">
+    <row r="16" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B16" s="158"/>
       <c r="C16" s="172" t="s">
         <v>323</v>
@@ -18995,7 +18995,7 @@
       <c r="F16" s="173"/>
       <c r="G16" s="159"/>
     </row>
-    <row r="17" spans="2:7" ht="18.75">
+    <row r="17" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B17" s="158"/>
       <c r="C17" s="172" t="s">
         <v>324</v>
@@ -19008,7 +19008,7 @@
       <c r="F17" s="173"/>
       <c r="G17" s="159"/>
     </row>
-    <row r="18" spans="2:7" ht="18.75">
+    <row r="18" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B18" s="158"/>
       <c r="C18" s="172" t="s">
         <v>325</v>
@@ -19021,7 +19021,7 @@
       <c r="F18" s="173"/>
       <c r="G18" s="159"/>
     </row>
-    <row r="19" spans="2:7" ht="15.75">
+    <row r="19" spans="2:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B19" s="158"/>
       <c r="C19" s="172" t="s">
         <v>326</v>
@@ -19039,7 +19039,7 @@
       </c>
       <c r="G19" s="159"/>
     </row>
-    <row r="20" spans="2:7" ht="18.75">
+    <row r="20" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B20" s="158"/>
       <c r="C20" s="175"/>
       <c r="D20" s="176"/>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="G20" s="159"/>
     </row>
-    <row r="21" spans="2:7">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B21" s="158"/>
       <c r="C21" s="169"/>
       <c r="D21" s="169"/>
@@ -19060,7 +19060,7 @@
       <c r="F21" s="169"/>
       <c r="G21" s="159"/>
     </row>
-    <row r="22" spans="2:7" ht="33" customHeight="1">
+    <row r="22" spans="2:7" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="158"/>
       <c r="C22" s="178" t="s">
         <v>328</v>
@@ -19073,7 +19073,7 @@
       <c r="F22" s="289"/>
       <c r="G22" s="159"/>
     </row>
-    <row r="23" spans="2:7" ht="41.45" customHeight="1">
+    <row r="23" spans="2:7" ht="41.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="158"/>
       <c r="C23" s="180"/>
       <c r="D23" s="179"/>
@@ -19083,7 +19083,7 @@
       </c>
       <c r="G23" s="159"/>
     </row>
-    <row r="24" spans="2:7" ht="18.75">
+    <row r="24" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B24" s="158"/>
       <c r="C24" s="290"/>
       <c r="D24" s="290"/>
@@ -19093,7 +19093,7 @@
       </c>
       <c r="G24" s="159"/>
     </row>
-    <row r="25" spans="2:7">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B25" s="184"/>
       <c r="C25" s="185"/>
       <c r="D25" s="185"/>
@@ -19101,7 +19101,7 @@
       <c r="F25" s="185"/>
       <c r="G25" s="186"/>
     </row>
-    <row r="26" spans="2:7">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="169"/>
       <c r="C26" s="169"/>
       <c r="D26" s="169"/>
@@ -19109,7 +19109,7 @@
       <c r="F26" s="169"/>
       <c r="G26" s="169"/>
     </row>
-    <row r="27" spans="2:7">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B27" s="169"/>
       <c r="C27" s="169"/>
       <c r="D27" s="169"/>
@@ -19117,7 +19117,7 @@
       <c r="F27" s="169"/>
       <c r="G27" s="169"/>
     </row>
-    <row r="28" spans="2:7">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="169"/>
       <c r="C28" s="169"/>
       <c r="D28" s="169"/>
@@ -19125,7 +19125,7 @@
       <c r="F28" s="169"/>
       <c r="G28" s="169"/>
     </row>
-    <row r="29" spans="2:7">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B29" s="169"/>
       <c r="C29" s="169"/>
       <c r="D29" s="169"/>
@@ -19133,7 +19133,7 @@
       <c r="F29" s="169"/>
       <c r="G29" s="169"/>
     </row>
-    <row r="30" spans="2:7">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="169"/>
       <c r="C30" s="169"/>
       <c r="D30" s="169"/>
@@ -19141,7 +19141,7 @@
       <c r="F30" s="169"/>
       <c r="G30" s="169"/>
     </row>
-    <row r="31" spans="2:7" ht="28.5">
+    <row r="31" spans="2:7" ht="29" x14ac:dyDescent="0.35">
       <c r="B31" s="156"/>
       <c r="C31" s="286" t="s">
         <v>163</v>
@@ -19151,7 +19151,7 @@
       <c r="F31" s="286"/>
       <c r="G31" s="157"/>
     </row>
-    <row r="32" spans="2:7" ht="15.75">
+    <row r="32" spans="2:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B32" s="158"/>
       <c r="C32" s="287" t="s">
         <v>303</v>
@@ -19161,7 +19161,7 @@
       <c r="F32" s="287"/>
       <c r="G32" s="159"/>
     </row>
-    <row r="33" spans="2:7" ht="21">
+    <row r="33" spans="2:7" ht="21" x14ac:dyDescent="0.25">
       <c r="B33" s="158"/>
       <c r="C33" s="288" t="s">
         <v>331</v>
@@ -19171,7 +19171,7 @@
       <c r="F33" s="288"/>
       <c r="G33" s="159"/>
     </row>
-    <row r="34" spans="2:7" ht="21">
+    <row r="34" spans="2:7" ht="21" x14ac:dyDescent="0.25">
       <c r="B34" s="158"/>
       <c r="C34" s="160"/>
       <c r="D34" s="161" t="s">
@@ -19186,7 +19186,7 @@
       </c>
       <c r="G34" s="159"/>
     </row>
-    <row r="35" spans="2:7" ht="18.75">
+    <row r="35" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B35" s="158"/>
       <c r="C35" s="164" t="s">
         <v>306</v>
@@ -19204,7 +19204,7 @@
       </c>
       <c r="G35" s="159"/>
     </row>
-    <row r="36" spans="2:7" ht="18.75">
+    <row r="36" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B36" s="158"/>
       <c r="C36" s="164" t="s">
         <v>179</v>
@@ -19222,7 +19222,7 @@
       </c>
       <c r="G36" s="159"/>
     </row>
-    <row r="37" spans="2:7" ht="18.75">
+    <row r="37" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B37" s="158"/>
       <c r="C37" s="164" t="s">
         <v>309</v>
@@ -19240,7 +19240,7 @@
       </c>
       <c r="G37" s="159"/>
     </row>
-    <row r="38" spans="2:7" ht="18.75" hidden="1">
+    <row r="38" spans="2:7" ht="19" hidden="1" x14ac:dyDescent="0.25">
       <c r="B38" s="158"/>
       <c r="C38" s="167" t="s">
         <v>311</v>
@@ -19258,7 +19258,7 @@
       </c>
       <c r="G38" s="159"/>
     </row>
-    <row r="39" spans="2:7">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B39" s="158"/>
       <c r="C39" s="169"/>
       <c r="D39" s="169"/>
@@ -19266,7 +19266,7 @@
       <c r="F39" s="169"/>
       <c r="G39" s="159"/>
     </row>
-    <row r="40" spans="2:7" ht="18.75">
+    <row r="40" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B40" s="158"/>
       <c r="C40" s="170" t="s">
         <v>313</v>
@@ -19278,7 +19278,7 @@
       <c r="F40" s="171"/>
       <c r="G40" s="159"/>
     </row>
-    <row r="41" spans="2:7" ht="18.75">
+    <row r="41" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B41" s="158"/>
       <c r="C41" s="172" t="s">
         <v>315</v>
@@ -19296,7 +19296,7 @@
       </c>
       <c r="G41" s="159"/>
     </row>
-    <row r="42" spans="2:7" ht="18.75">
+    <row r="42" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B42" s="158"/>
       <c r="C42" s="172" t="s">
         <v>317</v>
@@ -19314,7 +19314,7 @@
       </c>
       <c r="G42" s="159"/>
     </row>
-    <row r="43" spans="2:7" ht="18.75">
+    <row r="43" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B43" s="158"/>
       <c r="C43" s="172" t="s">
         <v>319</v>
@@ -19332,7 +19332,7 @@
       </c>
       <c r="G43" s="159"/>
     </row>
-    <row r="44" spans="2:7" ht="18.75">
+    <row r="44" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B44" s="158"/>
       <c r="C44" s="172" t="s">
         <v>321</v>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="G44" s="159"/>
     </row>
-    <row r="45" spans="2:7" ht="18.75">
+    <row r="45" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B45" s="158"/>
       <c r="C45" s="172" t="s">
         <v>323</v>
@@ -19363,7 +19363,7 @@
       <c r="F45" s="173"/>
       <c r="G45" s="159"/>
     </row>
-    <row r="46" spans="2:7" ht="18.75">
+    <row r="46" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B46" s="158"/>
       <c r="C46" s="172" t="s">
         <v>324</v>
@@ -19376,7 +19376,7 @@
       <c r="F46" s="173"/>
       <c r="G46" s="159"/>
     </row>
-    <row r="47" spans="2:7" ht="18.75">
+    <row r="47" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B47" s="158"/>
       <c r="C47" s="172" t="s">
         <v>332</v>
@@ -19389,7 +19389,7 @@
       <c r="F47" s="173"/>
       <c r="G47" s="159"/>
     </row>
-    <row r="48" spans="2:7" ht="15.75">
+    <row r="48" spans="2:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B48" s="158"/>
       <c r="C48" s="172" t="s">
         <v>326</v>
@@ -19407,7 +19407,7 @@
       </c>
       <c r="G48" s="159"/>
     </row>
-    <row r="49" spans="2:7" ht="18.75">
+    <row r="49" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B49" s="158"/>
       <c r="C49" s="175"/>
       <c r="D49" s="176"/>
@@ -19420,7 +19420,7 @@
       </c>
       <c r="G49" s="159"/>
     </row>
-    <row r="50" spans="2:7">
+    <row r="50" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B50" s="158"/>
       <c r="C50" s="169"/>
       <c r="D50" s="169"/>
@@ -19428,7 +19428,7 @@
       <c r="F50" s="169"/>
       <c r="G50" s="159"/>
     </row>
-    <row r="51" spans="2:7" ht="37.9" customHeight="1">
+    <row r="51" spans="2:7" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="158"/>
       <c r="C51" s="178" t="s">
         <v>328</v>
@@ -19441,7 +19441,7 @@
       <c r="F51" s="289"/>
       <c r="G51" s="159"/>
     </row>
-    <row r="52" spans="2:7" ht="41.45" customHeight="1">
+    <row r="52" spans="2:7" ht="41.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B52" s="158"/>
       <c r="C52" s="180"/>
       <c r="D52" s="179"/>
@@ -19451,7 +19451,7 @@
       </c>
       <c r="G52" s="159"/>
     </row>
-    <row r="53" spans="2:7" ht="18.75">
+    <row r="53" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B53" s="158"/>
       <c r="C53" s="290"/>
       <c r="D53" s="290"/>
@@ -19461,7 +19461,7 @@
       </c>
       <c r="G53" s="159"/>
     </row>
-    <row r="54" spans="2:7">
+    <row r="54" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B54" s="184"/>
       <c r="C54" s="185"/>
       <c r="D54" s="185"/>
@@ -19471,16 +19471,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="D51:F51"/>
     <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="C24:D24"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094499" right="0.23622047244094499" top="0.35433070866141703" bottom="0.35433070866141703" header="0.31496062992126" footer="0.31496062992126"/>
@@ -19491,17 +19491,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:J49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="3" max="3" width="45.42578125" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="3" max="3" width="45.5" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" customWidth="1"/>
+    <col min="9" max="9" width="11.5" customWidth="1"/>
+    <col min="10" max="10" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7">
+    <row r="1" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B1" s="99"/>
       <c r="C1" s="99"/>
       <c r="D1" s="99"/>
@@ -19509,7 +19509,7 @@
       <c r="F1" s="99"/>
       <c r="G1" s="99"/>
     </row>
-    <row r="2" spans="2:7">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B2" s="291" t="s">
         <v>333</v>
       </c>
@@ -19519,7 +19519,7 @@
       <c r="F2" s="291"/>
       <c r="G2" s="291"/>
     </row>
-    <row r="3" spans="2:7">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="99"/>
       <c r="C3" s="99"/>
       <c r="D3" s="99"/>
@@ -19529,7 +19529,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="4" spans="2:7">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="298"/>
       <c r="C4" s="101" t="s">
         <v>335</v>
@@ -19539,7 +19539,7 @@
       <c r="F4" s="102"/>
       <c r="G4" s="103"/>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="299"/>
       <c r="C5" s="104" t="s">
         <v>336</v>
@@ -19549,7 +19549,7 @@
       <c r="F5" s="105"/>
       <c r="G5" s="106"/>
     </row>
-    <row r="6" spans="2:7">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B6" s="299"/>
       <c r="C6" s="107" t="s">
         <v>337</v>
@@ -19559,7 +19559,7 @@
       <c r="F6" s="99"/>
       <c r="G6" s="108"/>
     </row>
-    <row r="7" spans="2:7">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B7" s="299"/>
       <c r="C7" s="107" t="s">
         <v>338</v>
@@ -19569,7 +19569,7 @@
       <c r="F7" s="99"/>
       <c r="G7" s="108"/>
     </row>
-    <row r="8" spans="2:7" ht="15.75">
+    <row r="8" spans="2:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B8" s="300"/>
       <c r="C8" s="109" t="s">
         <v>339</v>
@@ -19581,7 +19581,7 @@
       </c>
       <c r="G8" s="112"/>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9" s="113" t="s">
         <v>341</v>
       </c>
@@ -19591,7 +19591,7 @@
       <c r="F9" s="115"/>
       <c r="G9" s="116"/>
     </row>
-    <row r="10" spans="2:7">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="117" t="s">
         <v>342</v>
       </c>
@@ -19603,7 +19603,7 @@
       <c r="F10" s="118"/>
       <c r="G10" s="119"/>
     </row>
-    <row r="11" spans="2:7">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B11" s="120" t="s">
         <v>344</v>
       </c>
@@ -19613,7 +19613,7 @@
       <c r="F11" s="99"/>
       <c r="G11" s="108"/>
     </row>
-    <row r="12" spans="2:7">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="301" t="s">
         <v>345</v>
       </c>
@@ -19623,7 +19623,7 @@
       <c r="F12" s="99"/>
       <c r="G12" s="121"/>
     </row>
-    <row r="13" spans="2:7">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B13" s="301"/>
       <c r="C13" s="302"/>
       <c r="D13" s="99"/>
@@ -19631,7 +19631,7 @@
       <c r="F13" s="99"/>
       <c r="G13" s="121"/>
     </row>
-    <row r="14" spans="2:7">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="301"/>
       <c r="C14" s="302"/>
       <c r="D14" s="99"/>
@@ -19639,7 +19639,7 @@
       <c r="F14" s="99"/>
       <c r="G14" s="121"/>
     </row>
-    <row r="15" spans="2:7">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B15" s="122" t="s">
         <v>346</v>
       </c>
@@ -19649,7 +19649,7 @@
       <c r="F15" s="115"/>
       <c r="G15" s="124"/>
     </row>
-    <row r="16" spans="2:7">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="125" t="s">
         <v>347</v>
       </c>
@@ -19659,7 +19659,7 @@
       <c r="F16" s="110"/>
       <c r="G16" s="126"/>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B17" s="127" t="s">
         <v>348</v>
       </c>
@@ -19669,7 +19669,7 @@
       <c r="F17" s="115"/>
       <c r="G17" s="116"/>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B18" s="127" t="s">
         <v>349</v>
       </c>
@@ -19679,7 +19679,7 @@
       <c r="F18" s="115"/>
       <c r="G18" s="116"/>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" spans="2:10" ht="16" x14ac:dyDescent="0.2">
       <c r="B19" s="128" t="s">
         <v>350</v>
       </c>
@@ -19699,7 +19699,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B20" s="120" t="s">
         <v>356</v>
       </c>
@@ -19714,7 +19714,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="21" spans="2:10">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B21" s="120"/>
       <c r="C21" s="99"/>
       <c r="D21" s="99"/>
@@ -19722,7 +19722,7 @@
       <c r="F21" s="99"/>
       <c r="G21" s="108"/>
     </row>
-    <row r="22" spans="2:10">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B22" s="120"/>
       <c r="C22" s="99" t="s">
         <v>358</v>
@@ -19735,7 +19735,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="2:10">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B23" s="120"/>
       <c r="C23" s="99"/>
       <c r="D23" s="99"/>
@@ -19743,7 +19743,7 @@
       <c r="F23" s="99"/>
       <c r="G23" s="108"/>
     </row>
-    <row r="24" spans="2:10">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B24" s="120"/>
       <c r="C24" s="99"/>
       <c r="D24" s="99"/>
@@ -19751,7 +19751,7 @@
       <c r="F24" s="99"/>
       <c r="G24" s="108"/>
     </row>
-    <row r="25" spans="2:10">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B25" s="120"/>
       <c r="C25" s="99" t="s">
         <v>359</v>
@@ -19768,7 +19768,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="2:10">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B26" s="120"/>
       <c r="C26" s="99" t="s">
         <v>361</v>
@@ -19785,7 +19785,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="2:10">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B27" s="120"/>
       <c r="C27" s="99" t="s">
         <v>362</v>
@@ -19802,7 +19802,7 @@
       </c>
       <c r="J27" s="97"/>
     </row>
-    <row r="28" spans="2:10">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B28" s="120"/>
       <c r="C28" s="99" t="s">
         <v>363</v>
@@ -19820,7 +19820,7 @@
       </c>
       <c r="J28" s="97"/>
     </row>
-    <row r="29" spans="2:10">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B29" s="120"/>
       <c r="C29" s="99" t="s">
         <v>364</v>
@@ -19837,7 +19837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:10">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B30" s="120"/>
       <c r="C30" s="99"/>
       <c r="D30" s="99"/>
@@ -19845,7 +19845,7 @@
       <c r="F30" s="99"/>
       <c r="G30" s="108"/>
     </row>
-    <row r="31" spans="2:10" s="98" customFormat="1" ht="36.75" customHeight="1">
+    <row r="31" spans="2:10" s="98" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="135"/>
       <c r="C31" s="292" t="s">
         <v>365</v>
@@ -19860,7 +19860,7 @@
       <c r="I31" s="154"/>
       <c r="J31" s="155"/>
     </row>
-    <row r="32" spans="2:10">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B32" s="293" t="s">
         <v>366</v>
       </c>
@@ -19873,7 +19873,7 @@
       </c>
       <c r="I32" s="98"/>
     </row>
-    <row r="33" spans="2:7">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="137"/>
       <c r="C33" s="138"/>
       <c r="D33" s="138"/>
@@ -19881,7 +19881,7 @@
       <c r="F33" s="138"/>
       <c r="G33" s="139"/>
     </row>
-    <row r="34" spans="2:7">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="140" t="s">
         <v>367</v>
       </c>
@@ -19891,7 +19891,7 @@
       <c r="F34" s="143"/>
       <c r="G34" s="144"/>
     </row>
-    <row r="35" spans="2:7" ht="15.75">
+    <row r="35" spans="2:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B35" s="145"/>
       <c r="C35" s="146"/>
       <c r="D35" s="118"/>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="G35" s="119"/>
     </row>
-    <row r="36" spans="2:7" ht="15.75">
+    <row r="36" spans="2:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B36" s="120" t="s">
         <v>369</v>
       </c>
@@ -19911,7 +19911,7 @@
       <c r="F36" s="149"/>
       <c r="G36" s="108"/>
     </row>
-    <row r="37" spans="2:7" ht="15.75">
+    <row r="37" spans="2:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B37" s="120"/>
       <c r="C37" s="148"/>
       <c r="D37" s="99"/>
@@ -19919,7 +19919,7 @@
       <c r="F37" s="149"/>
       <c r="G37" s="108"/>
     </row>
-    <row r="38" spans="2:7" ht="15.75">
+    <row r="38" spans="2:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B38" s="120"/>
       <c r="C38" s="148"/>
       <c r="D38" s="99"/>
@@ -19927,7 +19927,7 @@
       <c r="F38" s="149"/>
       <c r="G38" s="108"/>
     </row>
-    <row r="39" spans="2:7" ht="15.75">
+    <row r="39" spans="2:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B39" s="120"/>
       <c r="C39" s="148"/>
       <c r="D39" s="99"/>
@@ -19935,7 +19935,7 @@
       <c r="F39" s="149"/>
       <c r="G39" s="108"/>
     </row>
-    <row r="40" spans="2:7" ht="15.75">
+    <row r="40" spans="2:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B40" s="137"/>
       <c r="C40" s="150"/>
       <c r="D40" s="138"/>
@@ -19945,7 +19945,7 @@
       </c>
       <c r="G40" s="139"/>
     </row>
-    <row r="41" spans="2:7">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B41" s="120"/>
       <c r="C41" s="99"/>
       <c r="D41" s="99"/>
@@ -19953,7 +19953,7 @@
       <c r="F41" s="99"/>
       <c r="G41" s="108"/>
     </row>
-    <row r="42" spans="2:7">
+    <row r="42" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B42" s="120" t="s">
         <v>371</v>
       </c>
@@ -19963,7 +19963,7 @@
       <c r="F42" s="99"/>
       <c r="G42" s="108"/>
     </row>
-    <row r="43" spans="2:7">
+    <row r="43" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B43" s="295" t="s">
         <v>372</v>
       </c>
@@ -19973,7 +19973,7 @@
       <c r="F43" s="296"/>
       <c r="G43" s="297"/>
     </row>
-    <row r="44" spans="2:7">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B44" s="99"/>
       <c r="C44" s="99"/>
       <c r="D44" s="99"/>
@@ -19981,7 +19981,7 @@
       <c r="F44" s="99"/>
       <c r="G44" s="99"/>
     </row>
-    <row r="45" spans="2:7">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B45" s="152"/>
       <c r="C45" s="99"/>
       <c r="D45" s="99"/>
@@ -19989,7 +19989,7 @@
       <c r="F45" s="99"/>
       <c r="G45" s="99"/>
     </row>
-    <row r="46" spans="2:7">
+    <row r="46" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B46" s="153" t="s">
         <v>373</v>
       </c>
@@ -19999,7 +19999,7 @@
       <c r="F46" s="99"/>
       <c r="G46" s="99"/>
     </row>
-    <row r="47" spans="2:7">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B47" s="99" t="s">
         <v>374</v>
       </c>
@@ -20009,7 +20009,7 @@
       <c r="F47" s="99"/>
       <c r="G47" s="99"/>
     </row>
-    <row r="48" spans="2:7">
+    <row r="48" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B48" s="99" t="s">
         <v>375</v>
       </c>
@@ -20019,7 +20019,7 @@
       <c r="F48" s="99"/>
       <c r="G48" s="99"/>
     </row>
-    <row r="49" spans="2:7">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B49" s="99"/>
       <c r="C49" s="99"/>
       <c r="D49" s="99"/>
@@ -20044,69 +20044,69 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B1:J37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="11.5703125" customWidth="1"/>
-    <col min="3" max="3" width="53.28515625" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="22.5703125" customWidth="1"/>
+    <col min="2" max="2" width="11.5" customWidth="1"/>
+    <col min="3" max="3" width="53.33203125" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" customWidth="1"/>
+    <col min="7" max="7" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7">
-      <c r="B1" s="327" t="s">
+    <row r="1" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B1" s="307" t="s">
         <v>333</v>
       </c>
-      <c r="C1" s="327"/>
-      <c r="D1" s="327"/>
-      <c r="E1" s="327"/>
-      <c r="F1" s="327"/>
-      <c r="G1" s="327"/>
+      <c r="C1" s="307"/>
+      <c r="D1" s="307"/>
+      <c r="E1" s="307"/>
+      <c r="F1" s="307"/>
+      <c r="G1" s="307"/>
     </row>
-    <row r="2" spans="2:7">
-      <c r="B2" s="328"/>
-      <c r="C2" s="328"/>
-      <c r="D2" s="328"/>
-      <c r="E2" s="328"/>
-      <c r="F2" s="328"/>
-      <c r="G2" s="328"/>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B2" s="308"/>
+      <c r="C2" s="308"/>
+      <c r="D2" s="308"/>
+      <c r="E2" s="308"/>
+      <c r="F2" s="308"/>
+      <c r="G2" s="308"/>
     </row>
-    <row r="3" spans="2:7">
-      <c r="B3" s="322"/>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B3" s="314"/>
       <c r="C3" s="80"/>
       <c r="D3" s="80"/>
       <c r="E3" s="80"/>
       <c r="F3" s="80"/>
       <c r="G3" s="81"/>
     </row>
-    <row r="4" spans="2:7">
-      <c r="B4" s="323"/>
-      <c r="C4" s="303" t="s">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B4" s="315"/>
+      <c r="C4" s="321" t="s">
         <v>335</v>
       </c>
-      <c r="D4" s="304"/>
-      <c r="E4" s="304"/>
-      <c r="F4" s="304"/>
-      <c r="G4" s="305"/>
+      <c r="D4" s="322"/>
+      <c r="E4" s="322"/>
+      <c r="F4" s="322"/>
+      <c r="G4" s="323"/>
     </row>
-    <row r="5" spans="2:7">
-      <c r="B5" s="323"/>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B5" s="315"/>
       <c r="C5" s="82"/>
       <c r="D5" s="82"/>
       <c r="E5" s="82"/>
       <c r="F5" s="82"/>
       <c r="G5" s="83"/>
     </row>
-    <row r="6" spans="2:7" ht="31.5" customHeight="1">
-      <c r="B6" s="324"/>
-      <c r="C6" s="306" t="s">
+    <row r="6" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="316"/>
+      <c r="C6" s="324" t="s">
         <v>376</v>
       </c>
-      <c r="D6" s="307"/>
-      <c r="E6" s="307"/>
-      <c r="F6" s="307"/>
-      <c r="G6" s="308"/>
+      <c r="D6" s="325"/>
+      <c r="E6" s="325"/>
+      <c r="F6" s="325"/>
+      <c r="G6" s="326"/>
     </row>
-    <row r="7" spans="2:7">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B7" s="84" t="s">
         <v>377</v>
       </c>
@@ -20120,11 +20120,11 @@
         <v>379</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
-      <c r="B8" s="309" t="s">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B8" s="327" t="s">
         <v>380</v>
       </c>
-      <c r="C8" s="310"/>
+      <c r="C8" s="328"/>
       <c r="D8" s="85"/>
       <c r="E8" s="85"/>
       <c r="F8" s="85" t="s">
@@ -20132,11 +20132,11 @@
       </c>
       <c r="G8" s="85"/>
     </row>
-    <row r="9" spans="2:7" ht="37.5" customHeight="1">
-      <c r="B9" s="311" t="s">
+    <row r="9" spans="2:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="312" t="s">
         <v>382</v>
       </c>
-      <c r="C9" s="312"/>
+      <c r="C9" s="313"/>
       <c r="D9" s="85"/>
       <c r="E9" s="85"/>
       <c r="F9" s="85" t="s">
@@ -20146,35 +20146,35 @@
         <v>384</v>
       </c>
     </row>
-    <row r="10" spans="2:7">
-      <c r="B10" s="313" t="s">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B10" s="303" t="s">
         <v>385</v>
       </c>
-      <c r="C10" s="314"/>
-      <c r="D10" s="325"/>
-      <c r="E10" s="325"/>
-      <c r="F10" s="325" t="s">
+      <c r="C10" s="304"/>
+      <c r="D10" s="317"/>
+      <c r="E10" s="317"/>
+      <c r="F10" s="317" t="s">
         <v>386</v>
       </c>
-      <c r="G10" s="325" t="s">
+      <c r="G10" s="317" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="11" spans="2:7">
-      <c r="B11" s="315" t="s">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B11" s="305" t="s">
         <v>388</v>
       </c>
-      <c r="C11" s="316"/>
-      <c r="D11" s="326"/>
-      <c r="E11" s="326"/>
-      <c r="F11" s="326"/>
-      <c r="G11" s="326"/>
+      <c r="C11" s="306"/>
+      <c r="D11" s="318"/>
+      <c r="E11" s="318"/>
+      <c r="F11" s="318"/>
+      <c r="G11" s="318"/>
     </row>
-    <row r="12" spans="2:7">
-      <c r="B12" s="317" t="s">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B12" s="309" t="s">
         <v>389</v>
       </c>
-      <c r="C12" s="318"/>
+      <c r="C12" s="311"/>
       <c r="D12" s="85"/>
       <c r="E12" s="85"/>
       <c r="F12" s="85" t="s">
@@ -20184,7 +20184,7 @@
         <v>996729</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="60">
+    <row r="13" spans="2:7" ht="60" x14ac:dyDescent="0.2">
       <c r="B13" s="319" t="s">
         <v>391</v>
       </c>
@@ -20198,7 +20198,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="14" spans="2:7">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="84"/>
       <c r="C14" s="85"/>
       <c r="D14" s="85"/>
@@ -20206,7 +20206,7 @@
       <c r="F14" s="85"/>
       <c r="G14" s="85"/>
     </row>
-    <row r="15" spans="2:7">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B15" s="88" t="s">
         <v>394</v>
       </c>
@@ -20226,7 +20226,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="16" spans="2:7">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="84"/>
       <c r="C16" s="85"/>
       <c r="D16" s="85"/>
@@ -20234,7 +20234,7 @@
       <c r="F16" s="85"/>
       <c r="G16" s="85"/>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B17" s="90">
         <v>1</v>
       </c>
@@ -20246,7 +20246,7 @@
       <c r="F17" s="85"/>
       <c r="G17" s="91"/>
     </row>
-    <row r="18" spans="2:10" ht="30">
+    <row r="18" spans="2:10" ht="30" x14ac:dyDescent="0.2">
       <c r="B18" s="84"/>
       <c r="C18" s="87" t="s">
         <v>399</v>
@@ -20256,7 +20256,7 @@
       <c r="F18" s="85"/>
       <c r="G18" s="91"/>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B19" s="90" t="s">
         <v>400</v>
       </c>
@@ -20268,7 +20268,7 @@
       <c r="F19" s="85"/>
       <c r="G19" s="91"/>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B20" s="90">
         <v>3</v>
       </c>
@@ -20283,7 +20283,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="21" spans="2:10">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B21" s="84"/>
       <c r="C21" s="85"/>
       <c r="D21" s="85"/>
@@ -20291,7 +20291,7 @@
       <c r="F21" s="85"/>
       <c r="G21" s="91"/>
     </row>
-    <row r="22" spans="2:10">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B22" s="84"/>
       <c r="C22" s="85"/>
       <c r="D22" s="85"/>
@@ -20299,7 +20299,7 @@
       <c r="F22" s="85"/>
       <c r="G22" s="91"/>
     </row>
-    <row r="23" spans="2:10">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B23" s="84"/>
       <c r="C23" s="85"/>
       <c r="D23" s="85"/>
@@ -20307,7 +20307,7 @@
       <c r="F23" s="85"/>
       <c r="G23" s="91"/>
     </row>
-    <row r="24" spans="2:10">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B24" s="84"/>
       <c r="C24" s="85"/>
       <c r="D24" s="85"/>
@@ -20315,7 +20315,7 @@
       <c r="F24" s="85"/>
       <c r="G24" s="91"/>
     </row>
-    <row r="25" spans="2:10">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B25" s="84"/>
       <c r="C25" s="92" t="s">
         <v>403</v>
@@ -20328,44 +20328,44 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="2:10">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B26" s="84"/>
       <c r="C26" s="85"/>
-      <c r="D26" s="317" t="s">
+      <c r="D26" s="309" t="s">
         <v>404</v>
       </c>
-      <c r="E26" s="321"/>
-      <c r="F26" s="318"/>
+      <c r="E26" s="310"/>
+      <c r="F26" s="311"/>
       <c r="G26" s="91" t="e">
         <f>G25*9%</f>
         <v>#REF!</v>
       </c>
       <c r="I26" s="95"/>
     </row>
-    <row r="27" spans="2:10">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B27" s="84"/>
       <c r="C27" s="85"/>
-      <c r="D27" s="317" t="s">
+      <c r="D27" s="309" t="s">
         <v>405</v>
       </c>
-      <c r="E27" s="321"/>
-      <c r="F27" s="318"/>
+      <c r="E27" s="310"/>
+      <c r="F27" s="311"/>
       <c r="G27" s="91" t="e">
         <f>G26</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="2:10">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B28" s="84"/>
       <c r="C28" s="85"/>
-      <c r="D28" s="317" t="s">
+      <c r="D28" s="309" t="s">
         <v>406</v>
       </c>
-      <c r="E28" s="321"/>
-      <c r="F28" s="318"/>
+      <c r="E28" s="310"/>
+      <c r="F28" s="311"/>
       <c r="G28" s="91"/>
     </row>
-    <row r="29" spans="2:10">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B29" s="84"/>
       <c r="C29" s="85"/>
       <c r="D29" s="85"/>
@@ -20375,7 +20375,7 @@
       <c r="I29" s="96"/>
       <c r="J29" s="97"/>
     </row>
-    <row r="30" spans="2:10">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B30" s="84"/>
       <c r="C30" s="85"/>
       <c r="D30" s="85"/>
@@ -20389,11 +20389,11 @@
       </c>
       <c r="I30" s="97"/>
     </row>
-    <row r="31" spans="2:10" ht="35.25" customHeight="1">
-      <c r="B31" s="311" t="s">
+    <row r="31" spans="2:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="312" t="s">
         <v>407</v>
       </c>
-      <c r="C31" s="312"/>
+      <c r="C31" s="313"/>
       <c r="D31" s="85"/>
       <c r="E31" s="85"/>
       <c r="F31" s="85"/>
@@ -20401,7 +20401,7 @@
       <c r="I31" s="97"/>
       <c r="J31" s="97"/>
     </row>
-    <row r="32" spans="2:10">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B32" s="84"/>
       <c r="C32" s="85"/>
       <c r="D32" s="85"/>
@@ -20409,7 +20409,7 @@
       <c r="F32" s="85"/>
       <c r="G32" s="85"/>
     </row>
-    <row r="33" spans="2:7">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="84"/>
       <c r="C33" s="85"/>
       <c r="D33" s="85"/>
@@ -20417,37 +20417,41 @@
       <c r="F33" s="85"/>
       <c r="G33" s="85"/>
     </row>
-    <row r="34" spans="2:7">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="84"/>
       <c r="C34" s="85"/>
       <c r="D34" s="85"/>
       <c r="E34" s="85"/>
-      <c r="F34" s="317" t="s">
+      <c r="F34" s="309" t="s">
         <v>408</v>
       </c>
-      <c r="G34" s="318"/>
+      <c r="G34" s="311"/>
     </row>
-    <row r="35" spans="2:7">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="84"/>
       <c r="C35" s="85"/>
       <c r="D35" s="85"/>
       <c r="E35" s="85"/>
-      <c r="F35" s="313"/>
-      <c r="G35" s="314"/>
+      <c r="F35" s="303"/>
+      <c r="G35" s="304"/>
     </row>
-    <row r="36" spans="2:7">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B36" s="84"/>
       <c r="C36" s="85"/>
       <c r="D36" s="85"/>
       <c r="E36" s="85"/>
-      <c r="F36" s="315"/>
-      <c r="G36" s="316"/>
+      <c r="F36" s="305"/>
+      <c r="G36" s="306"/>
     </row>
-    <row r="37" spans="2:7">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="F35:G36"/>
     <mergeCell ref="B1:G2"/>
     <mergeCell ref="D28:F28"/>
@@ -20464,10 +20468,6 @@
     <mergeCell ref="D26:F26"/>
     <mergeCell ref="D27:F27"/>
     <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -20480,27 +20480,27 @@
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:CD51"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="23.5703125" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" customWidth="1"/>
-    <col min="4" max="4" width="26.28515625" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" customWidth="1"/>
-    <col min="16" max="45" width="9.28515625" customWidth="1"/>
-    <col min="47" max="53" width="9.28515625" customWidth="1"/>
-    <col min="56" max="56" width="12.28515625" customWidth="1"/>
-    <col min="59" max="61" width="9.28515625" customWidth="1"/>
+    <col min="2" max="2" width="23.5" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+    <col min="4" max="4" width="26.33203125" customWidth="1"/>
+    <col min="8" max="8" width="13.5" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" customWidth="1"/>
+    <col min="16" max="45" width="9.33203125" customWidth="1"/>
+    <col min="47" max="53" width="9.33203125" customWidth="1"/>
+    <col min="56" max="56" width="12.33203125" customWidth="1"/>
+    <col min="59" max="61" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:79">
+    <row r="1" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A1" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="2" spans="1:79" s="1" customFormat="1" ht="79.5">
+    <row r="2" spans="1:79" s="1" customFormat="1" ht="80" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>168</v>
       </c>
@@ -20732,7 +20732,7 @@
       </c>
       <c r="CA2" s="79"/>
     </row>
-    <row r="3" spans="1:79">
+    <row r="3" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>11</v>
       </c>
@@ -20952,7 +20952,7 @@
       </c>
       <c r="CA3" s="8"/>
     </row>
-    <row r="4" spans="1:79">
+    <row r="4" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>12</v>
       </c>
@@ -21172,7 +21172,7 @@
       </c>
       <c r="CA4" s="8"/>
     </row>
-    <row r="6" spans="1:79">
+    <row r="6" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>428</v>
       </c>
@@ -21180,7 +21180,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="7" spans="1:79">
+    <row r="7" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>6</v>
       </c>
@@ -21400,7 +21400,7 @@
       </c>
       <c r="CA7" s="8"/>
     </row>
-    <row r="8" spans="1:79">
+    <row r="8" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>7</v>
       </c>
@@ -21618,7 +21618,7 @@
       </c>
       <c r="CA8" s="8"/>
     </row>
-    <row r="9" spans="1:79">
+    <row r="9" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>9</v>
       </c>
@@ -21838,7 +21838,7 @@
       </c>
       <c r="CA9" s="8"/>
     </row>
-    <row r="11" spans="1:79">
+    <row r="11" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>445</v>
       </c>
@@ -21846,7 +21846,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="12" spans="1:79">
+    <row r="12" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>4</v>
       </c>
@@ -22063,7 +22063,7 @@
       </c>
       <c r="CA12" s="8"/>
     </row>
-    <row r="14" spans="1:79">
+    <row r="14" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>451</v>
       </c>
@@ -22071,7 +22071,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="15" spans="1:79" s="1" customFormat="1" ht="79.5">
+    <row r="15" spans="1:79" s="1" customFormat="1" ht="80" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
         <v>168</v>
       </c>
@@ -22303,7 +22303,7 @@
       </c>
       <c r="CA15" s="79"/>
     </row>
-    <row r="16" spans="1:79">
+    <row r="16" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A16" s="8">
         <v>5</v>
       </c>
@@ -22525,7 +22525,7 @@
       </c>
       <c r="CA16" s="8"/>
     </row>
-    <row r="17" spans="1:82">
+    <row r="17" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A17" s="8">
         <v>7</v>
       </c>
@@ -22743,7 +22743,7 @@
       <c r="BZ17" s="8"/>
       <c r="CA17" s="8"/>
     </row>
-    <row r="19" spans="1:82">
+    <row r="19" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>468</v>
       </c>
@@ -22751,7 +22751,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="20" spans="1:82" s="1" customFormat="1" ht="79.5">
+    <row r="20" spans="1:82" s="1" customFormat="1" ht="80" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
         <v>168</v>
       </c>
@@ -22989,7 +22989,7 @@
       </c>
       <c r="CC20" s="79"/>
     </row>
-    <row r="21" spans="1:82">
+    <row r="21" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A21" s="8">
         <v>7</v>
       </c>
@@ -23214,7 +23214,7 @@
       <c r="CB21" s="8"/>
       <c r="CC21" s="8"/>
     </row>
-    <row r="22" spans="1:82">
+    <row r="22" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A22" s="8">
         <v>10</v>
       </c>
@@ -23439,7 +23439,7 @@
       <c r="CB22" s="8"/>
       <c r="CC22" s="8"/>
     </row>
-    <row r="24" spans="1:82">
+    <row r="24" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>485</v>
       </c>
@@ -23447,7 +23447,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="25" spans="1:82" s="1" customFormat="1" ht="79.5">
+    <row r="25" spans="1:82" s="1" customFormat="1" ht="80" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>168</v>
       </c>
@@ -23688,7 +23688,7 @@
       </c>
       <c r="CD25" s="79"/>
     </row>
-    <row r="26" spans="1:82" s="2" customFormat="1">
+    <row r="26" spans="1:82" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="16">
         <v>10</v>
       </c>
@@ -23914,7 +23914,7 @@
       <c r="CC26" s="16"/>
       <c r="CD26" s="16"/>
     </row>
-    <row r="27" spans="1:82" s="2" customFormat="1">
+    <row r="27" spans="1:82" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="16">
         <v>13</v>
       </c>
@@ -24143,7 +24143,7 @@
       <c r="CC27" s="16"/>
       <c r="CD27" s="16"/>
     </row>
-    <row r="29" spans="1:82">
+    <row r="29" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>495</v>
       </c>
@@ -24151,7 +24151,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="30" spans="1:82" s="2" customFormat="1">
+    <row r="30" spans="1:82" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="16">
         <v>7</v>
       </c>
@@ -24374,7 +24374,7 @@
       <c r="CB30" s="16"/>
       <c r="CC30" s="16"/>
     </row>
-    <row r="31" spans="1:82" s="2" customFormat="1">
+    <row r="31" spans="1:82" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="16">
         <v>8</v>
       </c>
@@ -24597,7 +24597,7 @@
       <c r="CB31" s="16"/>
       <c r="CC31" s="16"/>
     </row>
-    <row r="32" spans="1:82" s="2" customFormat="1">
+    <row r="32" spans="1:82" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="16">
         <v>11</v>
       </c>
@@ -24820,7 +24820,7 @@
       <c r="CB32" s="16"/>
       <c r="CC32" s="16"/>
     </row>
-    <row r="33" spans="1:81" s="3" customFormat="1">
+    <row r="33" spans="1:81" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="19">
         <v>16</v>
       </c>
@@ -25041,7 +25041,7 @@
       <c r="CB33" s="19"/>
       <c r="CC33" s="19"/>
     </row>
-    <row r="35" spans="1:81">
+    <row r="35" spans="1:81" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>524</v>
       </c>
@@ -25049,7 +25049,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="36" spans="1:81" s="1" customFormat="1" ht="79.5">
+    <row r="36" spans="1:81" s="1" customFormat="1" ht="80" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
         <v>168</v>
       </c>
@@ -25287,7 +25287,7 @@
       </c>
       <c r="CC36" s="79"/>
     </row>
-    <row r="37" spans="1:81" s="2" customFormat="1">
+    <row r="37" spans="1:81" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="16">
         <v>6</v>
       </c>
@@ -25512,7 +25512,7 @@
       <c r="CB37" s="16"/>
       <c r="CC37" s="16"/>
     </row>
-    <row r="38" spans="1:81" s="4" customFormat="1">
+    <row r="38" spans="1:81" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="25">
         <v>9</v>
       </c>
@@ -25739,7 +25739,7 @@
       <c r="CB38" s="25"/>
       <c r="CC38" s="25"/>
     </row>
-    <row r="40" spans="1:81">
+    <row r="40" spans="1:81" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>536</v>
       </c>
@@ -25747,7 +25747,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="41" spans="1:81" s="1" customFormat="1" ht="61.5" customHeight="1">
+    <row r="41" spans="1:81" s="1" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
         <v>168</v>
       </c>
@@ -25985,7 +25985,7 @@
       </c>
       <c r="CC41" s="79"/>
     </row>
-    <row r="42" spans="1:81" s="2" customFormat="1">
+    <row r="42" spans="1:81" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="16">
         <v>3</v>
       </c>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="CC42" s="16"/>
     </row>
-    <row r="44" spans="1:81">
+    <row r="44" spans="1:81" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>546</v>
       </c>
@@ -26222,7 +26222,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="45" spans="1:81" s="1" customFormat="1" ht="61.5" customHeight="1">
+    <row r="45" spans="1:81" s="1" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>168</v>
       </c>
@@ -26460,7 +26460,7 @@
       </c>
       <c r="CC45" s="79"/>
     </row>
-    <row r="46" spans="1:81" s="2" customFormat="1">
+    <row r="46" spans="1:81" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="16">
         <v>1</v>
       </c>
@@ -26687,7 +26687,7 @@
       </c>
       <c r="CC46" s="16"/>
     </row>
-    <row r="48" spans="1:81">
+    <row r="48" spans="1:81" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>551</v>
       </c>
@@ -26695,7 +26695,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="49" spans="1:81" s="1" customFormat="1" ht="61.5" customHeight="1">
+    <row r="49" spans="1:81" s="1" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>168</v>
       </c>
@@ -26933,7 +26933,7 @@
       </c>
       <c r="CC49" s="79"/>
     </row>
-    <row r="50" spans="1:81" s="2" customFormat="1" ht="15.75">
+    <row r="50" spans="1:81" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="16">
         <v>9</v>
       </c>
@@ -27156,7 +27156,7 @@
       <c r="CB50" s="16"/>
       <c r="CC50" s="16"/>
     </row>
-    <row r="51" spans="1:81" s="2" customFormat="1" ht="15.75">
+    <row r="51" spans="1:81" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="16">
         <v>10</v>
       </c>
